--- a/artfynd/A 41898-2026 artfynd.xlsx
+++ b/artfynd/A 41898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137279267</v>
       </c>
       <c r="B2" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137279380</v>
       </c>
       <c r="B3" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137279886</v>
       </c>
       <c r="B4" t="n">
-        <v>80619</v>
+        <v>80629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137279283</v>
       </c>
       <c r="B5" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137279324</v>
       </c>
       <c r="B6" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137279400</v>
       </c>
       <c r="B7" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137279417</v>
       </c>
       <c r="B8" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137279902</v>
       </c>
       <c r="B9" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137279959</v>
       </c>
       <c r="B10" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137280020</v>
       </c>
       <c r="B11" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137280171</v>
       </c>
       <c r="B12" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137280251</v>
       </c>
       <c r="B13" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137280283</v>
       </c>
       <c r="B14" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137280206</v>
       </c>
       <c r="B15" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 41898-2026 artfynd.xlsx
+++ b/artfynd/A 41898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137279267</v>
       </c>
       <c r="B2" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137279380</v>
       </c>
       <c r="B3" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137279886</v>
       </c>
       <c r="B4" t="n">
-        <v>80629</v>
+        <v>80632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137279283</v>
       </c>
       <c r="B5" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137279324</v>
       </c>
       <c r="B6" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137279400</v>
       </c>
       <c r="B7" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137279417</v>
       </c>
       <c r="B8" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137279902</v>
       </c>
       <c r="B9" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137279959</v>
       </c>
       <c r="B10" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137280020</v>
       </c>
       <c r="B11" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137280171</v>
       </c>
       <c r="B12" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137280251</v>
       </c>
       <c r="B13" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137280283</v>
       </c>
       <c r="B14" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137280206</v>
       </c>
       <c r="B15" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 41898-2026 artfynd.xlsx
+++ b/artfynd/A 41898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137279267</v>
       </c>
       <c r="B2" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137279380</v>
       </c>
       <c r="B3" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137279886</v>
       </c>
       <c r="B4" t="n">
-        <v>80632</v>
+        <v>80637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137279283</v>
       </c>
       <c r="B5" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137279324</v>
       </c>
       <c r="B6" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137279400</v>
       </c>
       <c r="B7" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137279417</v>
       </c>
       <c r="B8" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137279902</v>
       </c>
       <c r="B9" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137279959</v>
       </c>
       <c r="B10" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137280020</v>
       </c>
       <c r="B11" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137280171</v>
       </c>
       <c r="B12" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137280251</v>
       </c>
       <c r="B13" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137280206</v>
       </c>
       <c r="B15" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 41898-2026 artfynd.xlsx
+++ b/artfynd/A 41898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137279267</v>
       </c>
       <c r="B2" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137279380</v>
       </c>
       <c r="B3" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137279886</v>
       </c>
       <c r="B4" t="n">
-        <v>80637</v>
+        <v>80648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137279283</v>
       </c>
       <c r="B5" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137279324</v>
       </c>
       <c r="B6" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137279400</v>
       </c>
       <c r="B7" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137279417</v>
       </c>
       <c r="B8" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137279902</v>
       </c>
       <c r="B9" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137279959</v>
       </c>
       <c r="B10" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137280020</v>
       </c>
       <c r="B11" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137280171</v>
       </c>
       <c r="B12" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137280251</v>
       </c>
       <c r="B13" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41898-2026 artfynd.xlsx
+++ b/artfynd/A 41898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137279267</v>
       </c>
       <c r="B2" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137279380</v>
       </c>
       <c r="B3" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137279886</v>
       </c>
       <c r="B4" t="n">
-        <v>80648</v>
+        <v>80649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137279283</v>
       </c>
       <c r="B5" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137279324</v>
       </c>
       <c r="B6" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137279400</v>
       </c>
       <c r="B7" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137279417</v>
       </c>
       <c r="B8" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137279902</v>
       </c>
       <c r="B9" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137279959</v>
       </c>
       <c r="B10" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137280020</v>
       </c>
       <c r="B11" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137280171</v>
       </c>
       <c r="B12" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137280251</v>
       </c>
       <c r="B13" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41898-2026 artfynd.xlsx
+++ b/artfynd/A 41898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137279267</v>
       </c>
       <c r="B2" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137279380</v>
       </c>
       <c r="B3" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137279886</v>
       </c>
       <c r="B4" t="n">
-        <v>80649</v>
+        <v>80651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137279283</v>
       </c>
       <c r="B5" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137279324</v>
       </c>
       <c r="B6" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137279400</v>
       </c>
       <c r="B7" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137279417</v>
       </c>
       <c r="B8" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137279902</v>
       </c>
       <c r="B9" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137279959</v>
       </c>
       <c r="B10" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137280020</v>
       </c>
       <c r="B11" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137280171</v>
       </c>
       <c r="B12" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137280251</v>
       </c>
       <c r="B13" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 41898-2026 artfynd.xlsx
+++ b/artfynd/A 41898-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137279267</v>
       </c>
       <c r="B2" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137279380</v>
       </c>
       <c r="B3" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137279886</v>
       </c>
       <c r="B4" t="n">
-        <v>80651</v>
+        <v>80655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137279283</v>
       </c>
       <c r="B5" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>137279324</v>
       </c>
       <c r="B6" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>137279400</v>
       </c>
       <c r="B7" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>137279417</v>
       </c>
       <c r="B8" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>137279902</v>
       </c>
       <c r="B9" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>137279959</v>
       </c>
       <c r="B10" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>137280020</v>
       </c>
       <c r="B11" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>137280171</v>
       </c>
       <c r="B12" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1805,7 +1805,7 @@
         <v>137280251</v>
       </c>
       <c r="B13" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
         <v>137280283</v>
       </c>
       <c r="B14" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>137280206</v>
       </c>
       <c r="B15" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
